--- a/src/xlsx/data.xlsx
+++ b/src/xlsx/data.xlsx
@@ -991,7 +991,7 @@
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>尼多後@@@@</t>
+          <t>尼多后@@@@</t>
         </is>
       </c>
       <c r="F17" s="1" t="inlineStr">
@@ -5840,7 +5840,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>高階球</t>
+          <t>高級球</t>
         </is>
       </c>
       <c r="K3" s="0" t="inlineStr">
@@ -6347,7 +6347,7 @@
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>秘金鑰匙</t>
+          <t>秘密鑰匙</t>
         </is>
       </c>
     </row>
